--- a/backtest_runs/20260410_193731/by_symbol/HUSI/HUSI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HUSI/HUSI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-14005.04999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>85994.95000000001</v>
@@ -587,7 +587,7 @@
         <v>-3376.56000000001</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>82618.39</v>
@@ -633,7 +633,7 @@
         <v>-2110.350000000003</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>80508.03999999999</v>
@@ -679,7 +679,7 @@
         <v>-10935.44999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>69572.59</v>
@@ -771,7 +771,7 @@
         <v>-2263.829999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>72987.51999999999</v>
@@ -909,7 +909,7 @@
         <v>-10206.42</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>67500.60999999999</v>
@@ -1001,7 +1001,7 @@
         <v>-6177.569999999998</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>61323.03999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-1496.430000000002</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>59826.60999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-10551.75</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>60977.70999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-8364.659999999998</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>62052.07</v>
